--- a/data/trans_orig/P39C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P39C-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2016 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53059</t>
+          <t>52186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83136</t>
+          <t>83160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35947</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63625</t>
+          <t>64300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96336</t>
+          <t>94733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138417</t>
+          <t>136864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112224</t>
+          <t>112682</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152047</t>
+          <t>151665</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134227</t>
+          <t>136215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183074</t>
+          <t>187112</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>259711</t>
+          <t>258876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>321862</t>
+          <t>322315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>164149</t>
+          <t>162627</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>209801</t>
+          <t>208422</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>253114</t>
+          <t>250753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>308044</t>
+          <t>311982</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>424851</t>
+          <t>430939</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>500468</t>
+          <t>505936</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90475</t>
+          <t>91098</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127970</t>
+          <t>127568</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>153386</t>
+          <t>152416</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205027</t>
+          <t>204260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258672</t>
+          <t>257436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>317301</t>
+          <t>318085</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133677</t>
+          <t>133713</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174020</t>
+          <t>176230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210225</t>
+          <t>212771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>267328</t>
+          <t>267863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>356029</t>
+          <t>355602</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>426666</t>
+          <t>431213</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165981</t>
+          <t>166197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>217592</t>
+          <t>220176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142675</t>
+          <t>141041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190004</t>
+          <t>192653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>318323</t>
+          <t>325383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>388500</t>
+          <t>392357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>426583</t>
+          <t>426188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500274</t>
+          <t>498354</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>444565</t>
+          <t>443459</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516906</t>
+          <t>519676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>886089</t>
+          <t>891928</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>993478</t>
+          <t>992647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>434182</t>
+          <t>434931</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>508263</t>
+          <t>505593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>456766</t>
+          <t>458400</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>533232</t>
+          <t>528515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>912892</t>
+          <t>909138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1019210</t>
+          <t>1017937</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173210</t>
+          <t>176573</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>229620</t>
+          <t>231128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>165310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220506</t>
+          <t>217348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>361623</t>
+          <t>356360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>434617</t>
+          <t>433527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>207955</t>
+          <t>206354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265894</t>
+          <t>265323</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284373</t>
+          <t>279824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348657</t>
+          <t>348645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>506442</t>
+          <t>504861</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>596831</t>
+          <t>591874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41101</t>
+          <t>41376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70167</t>
+          <t>70911</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26481</t>
+          <t>26115</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50774</t>
+          <t>49687</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72855</t>
+          <t>74192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110030</t>
+          <t>109889</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111941</t>
+          <t>112720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152604</t>
+          <t>152922</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118481</t>
+          <t>116420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158400</t>
+          <t>154310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>240203</t>
+          <t>241595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297303</t>
+          <t>296445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90992</t>
+          <t>90003</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130350</t>
+          <t>127830</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117395</t>
+          <t>119505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158652</t>
+          <t>157747</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>218980</t>
+          <t>218629</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>273620</t>
+          <t>276214</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>36398</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66526</t>
+          <t>65305</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45901</t>
+          <t>44728</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74916</t>
+          <t>76321</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89573</t>
+          <t>90819</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132394</t>
+          <t>133589</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60201</t>
+          <t>62380</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95111</t>
+          <t>95649</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59771</t>
+          <t>61543</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91727</t>
+          <t>94425</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132391</t>
+          <t>130858</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>181643</t>
+          <t>176848</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>279547</t>
+          <t>276495</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>347300</t>
+          <t>345433</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>221647</t>
+          <t>222670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>282809</t>
+          <t>283936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>519322</t>
+          <t>520532</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>609514</t>
+          <t>612573</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>679242</t>
+          <t>677235</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>768658</t>
+          <t>772067</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>726762</t>
+          <t>731482</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>826958</t>
+          <t>823655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1434738</t>
+          <t>1432960</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1572699</t>
+          <t>1568417</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>715110</t>
+          <t>712328</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>810848</t>
+          <t>807978</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>862754</t>
+          <t>862918</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>963191</t>
+          <t>964313</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1607874</t>
+          <t>1605373</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1743782</t>
+          <t>1743836</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>327215</t>
+          <t>325246</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>402720</t>
+          <t>397771</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>388188</t>
+          <t>387945</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>470153</t>
+          <t>468978</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>741394</t>
+          <t>730726</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>846821</t>
+          <t>837511</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>426445</t>
+          <t>428765</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>503661</t>
+          <t>509180</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>582609</t>
+          <t>583625</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>672069</t>
+          <t>672896</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1030675</t>
+          <t>1030048</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1152247</t>
+          <t>1156159</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2023 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22910</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44135</t>
+          <t>43304</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39260</t>
+          <t>39665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49503</t>
+          <t>48782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75435</t>
+          <t>74859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74271</t>
+          <t>76064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106369</t>
+          <t>106906</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,47 +3818,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>128404</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>113294</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>145104</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>18,54%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>16,36%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>23,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>128404</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>114445</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>145655</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>16,53%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196125</t>
+          <t>196508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>240874</t>
+          <t>241950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94854</t>
+          <t>93953</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>125907</t>
+          <t>127631</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>182291</t>
+          <t>181979</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>217553</t>
+          <t>219105</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>287792</t>
+          <t>285820</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>337320</t>
+          <t>334974</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85740</t>
+          <t>85619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118944</t>
+          <t>118505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127273</t>
+          <t>126199</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156485</t>
+          <t>157326</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>221856</t>
+          <t>220362</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>266074</t>
+          <t>267734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105218</t>
+          <t>102530</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137058</t>
+          <t>136528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>176318</t>
+          <t>177091</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210570</t>
+          <t>210389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>288553</t>
+          <t>287311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336566</t>
+          <t>337889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129884</t>
+          <t>127490</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188446</t>
+          <t>182795</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100006</t>
+          <t>101338</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176307</t>
+          <t>175513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>244819</t>
+          <t>241808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340970</t>
+          <t>338158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>393408</t>
+          <t>397823</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479156</t>
+          <t>479641</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>294647</t>
+          <t>303768</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>501449</t>
+          <t>505392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>677538</t>
+          <t>673837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>943671</t>
+          <t>942656</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>429364</t>
+          <t>430706</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>508986</t>
+          <t>513496</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>539405</t>
+          <t>536673</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1069278</t>
+          <t>1078597</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1005627</t>
+          <t>1004591</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1641373</t>
+          <t>1628814</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>210804</t>
+          <t>208906</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>269483</t>
+          <t>270101</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155925</t>
+          <t>158456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>271988</t>
+          <t>274195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>387933</t>
+          <t>387181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>523767</t>
+          <t>520748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237088</t>
+          <t>239110</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295293</t>
+          <t>296191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>225933</t>
+          <t>224805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>389144</t>
+          <t>392079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>473592</t>
+          <t>482754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>657638</t>
+          <t>658758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>23544</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47416</t>
+          <t>49187</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50978</t>
+          <t>51344</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57954</t>
+          <t>57587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91067</t>
+          <t>92343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122115</t>
+          <t>123042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165313</t>
+          <t>167087</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120032</t>
+          <t>121036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157382</t>
+          <t>156780</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254756</t>
+          <t>250988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308619</t>
+          <t>311645</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>151893</t>
+          <t>150150</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>196273</t>
+          <t>193736</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>160082</t>
+          <t>160124</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>198657</t>
+          <t>197982</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>323498</t>
+          <t>319129</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>382460</t>
+          <t>381185</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70501</t>
+          <t>68251</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102350</t>
+          <t>103221</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80950</t>
+          <t>79928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109491</t>
+          <t>109485</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158282</t>
+          <t>159174</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201829</t>
+          <t>202582</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81056</t>
+          <t>80591</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116815</t>
+          <t>116713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114711</t>
+          <t>115067</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150351</t>
+          <t>150938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205959</t>
+          <t>204149</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>256092</t>
+          <t>254790</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>187076</t>
+          <t>188745</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>252785</t>
+          <t>255717</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>171688</t>
+          <t>170937</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>242939</t>
+          <t>246887</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>378949</t>
+          <t>378201</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>478693</t>
+          <t>480175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>618293</t>
+          <t>615317</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>717700</t>
+          <t>718684</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>539657</t>
+          <t>561940</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>769233</t>
+          <t>768158</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1197486</t>
+          <t>1200068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1449551</t>
+          <t>1449599</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>704436</t>
+          <t>697902</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>802390</t>
+          <t>798679</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>921201</t>
+          <t>912331</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1583496</t>
+          <t>1508982</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1658153</t>
+          <t>1667969</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2273969</t>
+          <t>2291945</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>387905</t>
+          <t>384923</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>463098</t>
+          <t>464673</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>368019</t>
+          <t>377856</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>513195</t>
+          <t>518754</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>787739</t>
+          <t>798949</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>958371</t>
+          <t>951122</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>448129</t>
+          <t>447931</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>523485</t>
+          <t>527689</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>509392</t>
+          <t>529350</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>721382</t>
+          <t>725878</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1027878</t>
+          <t>1005316</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1220467</t>
+          <t>1211294</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P39C-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52186</t>
+          <t>53224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83160</t>
+          <t>85127</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>35678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64300</t>
+          <t>65704</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94733</t>
+          <t>94975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136864</t>
+          <t>137656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112682</t>
+          <t>111654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151665</t>
+          <t>151970</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136215</t>
+          <t>136414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>187112</t>
+          <t>185602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>258876</t>
+          <t>259824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>322315</t>
+          <t>321116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>162627</t>
+          <t>161636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>208422</t>
+          <t>206901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>250753</t>
+          <t>254180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311982</t>
+          <t>311614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>430939</t>
+          <t>431627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>505936</t>
+          <t>503757</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91098</t>
+          <t>91561</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127568</t>
+          <t>129022</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>152416</t>
+          <t>152742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204260</t>
+          <t>204479</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257436</t>
+          <t>251664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>318085</t>
+          <t>317769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133713</t>
+          <t>133792</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176230</t>
+          <t>175171</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>212771</t>
+          <t>212553</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>267863</t>
+          <t>269843</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>355602</t>
+          <t>356821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>431213</t>
+          <t>426783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>166197</t>
+          <t>165158</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>220176</t>
+          <t>217525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141041</t>
+          <t>140293</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192653</t>
+          <t>189701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>325383</t>
+          <t>319360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>392357</t>
+          <t>392412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>426188</t>
+          <t>427718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>498354</t>
+          <t>499189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443459</t>
+          <t>443913</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>519676</t>
+          <t>516165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>891928</t>
+          <t>891321</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>992647</t>
+          <t>994061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>434931</t>
+          <t>434166</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>505593</t>
+          <t>508224</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>458400</t>
+          <t>452899</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>528515</t>
+          <t>531452</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>909138</t>
+          <t>914277</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1017937</t>
+          <t>1022717</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176573</t>
+          <t>176603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165310</t>
+          <t>167802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>217348</t>
+          <t>222259</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>356360</t>
+          <t>357870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>433527</t>
+          <t>431847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206354</t>
+          <t>206761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265323</t>
+          <t>261761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>279824</t>
+          <t>284133</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348645</t>
+          <t>347021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>504861</t>
+          <t>503190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>591874</t>
+          <t>594106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41376</t>
+          <t>41722</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70911</t>
+          <t>70254</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26115</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>49989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74192</t>
+          <t>73829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109889</t>
+          <t>109418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112720</t>
+          <t>111091</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152922</t>
+          <t>150526</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116420</t>
+          <t>120836</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154310</t>
+          <t>159797</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>241595</t>
+          <t>239886</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>296445</t>
+          <t>296647</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>127830</t>
+          <t>129692</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>119505</t>
+          <t>115416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157747</t>
+          <t>154787</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>218629</t>
+          <t>219171</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>276214</t>
+          <t>273861</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36398</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65305</t>
+          <t>67246</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44728</t>
+          <t>45919</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76321</t>
+          <t>74786</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90819</t>
+          <t>91473</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133589</t>
+          <t>132747</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62380</t>
+          <t>62465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95649</t>
+          <t>96001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61543</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>94425</t>
+          <t>93193</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130858</t>
+          <t>132865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>176848</t>
+          <t>179234</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>276495</t>
+          <t>278979</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>345433</t>
+          <t>346785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>222670</t>
+          <t>220978</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283936</t>
+          <t>281348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>520532</t>
+          <t>520401</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>612573</t>
+          <t>610190</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>677235</t>
+          <t>675577</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>772067</t>
+          <t>772490</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>731482</t>
+          <t>729224</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>823655</t>
+          <t>825231</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1432960</t>
+          <t>1438274</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1568417</t>
+          <t>1574781</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>712328</t>
+          <t>719579</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>807978</t>
+          <t>813027</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>862918</t>
+          <t>860938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>964313</t>
+          <t>961063</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1605373</t>
+          <t>1607815</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1743836</t>
+          <t>1736988</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>325246</t>
+          <t>329794</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>397771</t>
+          <t>399284</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>387945</t>
+          <t>391763</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>468978</t>
+          <t>468720</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>730726</t>
+          <t>739972</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>837511</t>
+          <t>839565</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>428765</t>
+          <t>428077</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>509180</t>
+          <t>507354</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>583625</t>
+          <t>585300</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>672896</t>
+          <t>672180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1030048</t>
+          <t>1033480</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1156159</t>
+          <t>1156492</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -3685,32 +3685,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31578</t>
+          <t>37393</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43304</t>
+          <t>50621</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3720,32 +3720,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>32668</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>24368</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3755,32 +3755,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>61414</t>
+          <t>70061</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48782</t>
+          <t>55669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74859</t>
+          <t>86130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -3798,32 +3798,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90754</t>
+          <t>101492</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76064</t>
+          <t>84846</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106906</t>
+          <t>121005</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3833,32 +3833,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>128404</t>
+          <t>139175</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113294</t>
+          <t>123969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145104</t>
+          <t>158597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3868,32 +3868,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>219159</t>
+          <t>240666</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196508</t>
+          <t>218404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241950</t>
+          <t>265964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>110641</t>
+          <t>122829</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93953</t>
+          <t>105884</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127631</t>
+          <t>144407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3946,32 +3946,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>200110</t>
+          <t>223282</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>181979</t>
+          <t>204928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>219105</t>
+          <t>243586</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3981,32 +3981,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>310751</t>
+          <t>346111</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>285820</t>
+          <t>321649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>334974</t>
+          <t>372986</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -4024,32 +4024,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>101138</t>
+          <t>107859</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85619</t>
+          <t>91410</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118505</t>
+          <t>124544</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4059,32 +4059,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>141802</t>
+          <t>154982</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126199</t>
+          <t>138467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157326</t>
+          <t>171674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4094,32 +4094,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>242940</t>
+          <t>262841</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>220362</t>
+          <t>239565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>267734</t>
+          <t>284665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -4137,32 +4137,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>119751</t>
+          <t>125885</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102530</t>
+          <t>110505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136528</t>
+          <t>144301</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4172,32 +4172,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>192257</t>
+          <t>205964</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177091</t>
+          <t>187410</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210389</t>
+          <t>226865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4207,32 +4207,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>312008</t>
+          <t>331849</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>287311</t>
+          <t>306923</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>337889</t>
+          <t>358272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -4250,17 +4250,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>453863</t>
+          <t>495458</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>453863</t>
+          <t>495458</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>453863</t>
+          <t>495458</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4285,17 +4285,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>692409</t>
+          <t>756070</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>692409</t>
+          <t>756070</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>692409</t>
+          <t>756070</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1146272</t>
+          <t>1251528</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1146272</t>
+          <t>1251528</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1146272</t>
+          <t>1251528</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4367,32 +4367,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>154098</t>
+          <t>171870</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127490</t>
+          <t>146626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182795</t>
+          <t>202696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4402,32 +4402,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>146015</t>
+          <t>157532</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101338</t>
+          <t>136352</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175513</t>
+          <t>180325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4437,32 +4437,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>300113</t>
+          <t>329402</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>241808</t>
+          <t>296465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338158</t>
+          <t>370655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -4480,32 +4480,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>433380</t>
+          <t>466406</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>397823</t>
+          <t>427226</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479641</t>
+          <t>506554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4515,32 +4515,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>433152</t>
+          <t>479834</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>303768</t>
+          <t>445285</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>505392</t>
+          <t>513094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4550,32 +4550,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>866532</t>
+          <t>946240</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>673837</t>
+          <t>889982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>942656</t>
+          <t>998030</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>469427</t>
+          <t>493964</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>430706</t>
+          <t>453602</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>513496</t>
+          <t>535962</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4628,32 +4628,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>702946</t>
+          <t>515167</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>536673</t>
+          <t>484576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1078597</t>
+          <t>551999</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4663,32 +4663,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1172373</t>
+          <t>1009131</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1004591</t>
+          <t>959958</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1628814</t>
+          <t>1062270</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -4706,32 +4706,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>239079</t>
+          <t>260155</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>208906</t>
+          <t>232718</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>270101</t>
+          <t>292991</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4741,32 +4741,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>233089</t>
+          <t>257851</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158456</t>
+          <t>233752</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>274195</t>
+          <t>283198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4776,32 +4776,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>472168</t>
+          <t>518006</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>387181</t>
+          <t>480390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>520748</t>
+          <t>561553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -4819,32 +4819,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>265626</t>
+          <t>283916</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239110</t>
+          <t>253103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296191</t>
+          <t>316811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4854,32 +4854,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>336471</t>
+          <t>378386</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224805</t>
+          <t>343356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>392079</t>
+          <t>410969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4889,32 +4889,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>602097</t>
+          <t>662302</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>482754</t>
+          <t>619630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>658758</t>
+          <t>708117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -4932,17 +4932,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1561611</t>
+          <t>1676311</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1561611</t>
+          <t>1676311</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1561611</t>
+          <t>1676311</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4967,17 +4967,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1851673</t>
+          <t>1788770</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1851673</t>
+          <t>1788770</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1851673</t>
+          <t>1788770</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5002,17 +5002,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3413284</t>
+          <t>3465080</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3413284</t>
+          <t>3465080</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3413284</t>
+          <t>3465080</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5049,32 +5049,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>33775</t>
+          <t>38779</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23544</t>
+          <t>26755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49187</t>
+          <t>52981</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5084,32 +5084,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38831</t>
+          <t>41239</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51344</t>
+          <t>53314</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5119,32 +5119,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>72607</t>
+          <t>80018</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57587</t>
+          <t>64733</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92343</t>
+          <t>100635</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -5162,32 +5162,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>142637</t>
+          <t>160552</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123042</t>
+          <t>138266</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167087</t>
+          <t>185261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5197,32 +5197,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>138212</t>
+          <t>156670</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121036</t>
+          <t>138245</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156780</t>
+          <t>175818</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5232,32 +5232,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>280849</t>
+          <t>317222</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>250988</t>
+          <t>288287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>311645</t>
+          <t>348206</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>171733</t>
+          <t>188133</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>150150</t>
+          <t>161719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193736</t>
+          <t>211035</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5310,32 +5310,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>178451</t>
+          <t>195623</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>160124</t>
+          <t>174276</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>197982</t>
+          <t>215960</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5345,32 +5345,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>350184</t>
+          <t>383756</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>319129</t>
+          <t>351664</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>381185</t>
+          <t>415363</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -5388,32 +5388,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>84870</t>
+          <t>94035</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68251</t>
+          <t>77291</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103221</t>
+          <t>112151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5423,32 +5423,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>94723</t>
+          <t>109582</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79928</t>
+          <t>93912</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>126870</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5458,32 +5458,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>179594</t>
+          <t>203617</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>159174</t>
+          <t>179781</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>202582</t>
+          <t>228433</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -5501,17 +5501,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>97883</t>
+          <t>108878</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80591</t>
+          <t>91434</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116713</t>
+          <t>129387</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>132250</t>
+          <t>147226</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115067</t>
+          <t>127636</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150938</t>
+          <t>166249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5571,32 +5571,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>230133</t>
+          <t>256104</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204149</t>
+          <t>229789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>254790</t>
+          <t>286186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -5614,17 +5614,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>530898</t>
+          <t>590377</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>530898</t>
+          <t>590377</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>530898</t>
+          <t>590377</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5649,17 +5649,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>582467</t>
+          <t>650340</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>582467</t>
+          <t>650340</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>582467</t>
+          <t>650340</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5684,17 +5684,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1113365</t>
+          <t>1240717</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1113365</t>
+          <t>1240717</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1113365</t>
+          <t>1240717</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5731,32 +5731,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>219452</t>
+          <t>248042</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188745</t>
+          <t>218296</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>255717</t>
+          <t>283222</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5766,32 +5766,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>214681</t>
+          <t>231439</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>170937</t>
+          <t>207854</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>246887</t>
+          <t>262354</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5801,32 +5801,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>434133</t>
+          <t>479481</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>378201</t>
+          <t>438512</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>480175</t>
+          <t>525373</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -5844,32 +5844,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>666772</t>
+          <t>728449</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>615317</t>
+          <t>678680</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>718684</t>
+          <t>776088</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5879,32 +5879,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>699768</t>
+          <t>775679</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>561940</t>
+          <t>732118</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>768158</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5914,32 +5914,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1366539</t>
+          <t>1504128</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1200068</t>
+          <t>1432501</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1449599</t>
+          <t>1571803</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>751800</t>
+          <t>804926</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>697902</t>
+          <t>754515</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>798679</t>
+          <t>853160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5992,32 +5992,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1081507</t>
+          <t>934072</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>912331</t>
+          <t>887481</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1508982</t>
+          <t>976680</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6027,32 +6027,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1833308</t>
+          <t>1738998</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1667969</t>
+          <t>1672044</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2291945</t>
+          <t>1805699</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -6070,32 +6070,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>425088</t>
+          <t>462049</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>384923</t>
+          <t>423787</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>464673</t>
+          <t>508554</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6105,32 +6105,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>469614</t>
+          <t>522414</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>377856</t>
+          <t>490383</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>518754</t>
+          <t>557593</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6140,32 +6140,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>894702</t>
+          <t>984463</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>798949</t>
+          <t>930392</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>951122</t>
+          <t>1035624</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -6183,32 +6183,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>483261</t>
+          <t>518679</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>447931</t>
+          <t>480865</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>527689</t>
+          <t>558694</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6218,32 +6218,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>660978</t>
+          <t>731575</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>529350</t>
+          <t>693519</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>725878</t>
+          <t>776019</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6253,32 +6253,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1144239</t>
+          <t>1250255</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1005316</t>
+          <t>1195162</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1211294</t>
+          <t>1312567</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -6296,17 +6296,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2546373</t>
+          <t>2762146</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2546373</t>
+          <t>2762146</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2546373</t>
+          <t>2762146</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6331,17 +6331,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3126549</t>
+          <t>3195179</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3126549</t>
+          <t>3195179</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3126549</t>
+          <t>3195179</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5672921</t>
+          <t>5957325</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5672921</t>
+          <t>5957325</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5672921</t>
+          <t>5957325</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
